--- a/xls/square_un_16_tri3_22.xlsx
+++ b/xls/square_un_16_tri3_22.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>668</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>340</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>564</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>3138</v>
+      </c>
+      <c r="I20">
+        <v>-7.728510017020902e-5</v>
+      </c>
+      <c r="J20">
+        <v>-0.23094000593717381</v>
+      </c>
+      <c r="K20">
+        <v>3.2357765754730337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>668</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>340</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>598</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>3330</v>
+      </c>
+      <c r="I21">
+        <v>-1.1588589233589868e-5</v>
+      </c>
+      <c r="J21">
+        <v>-0.035195672959569886</v>
+      </c>
+      <c r="K21">
+        <v>3.3554678787833194</v>
+      </c>
+    </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>11</v>
       </c>
       <c r="B22">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-2.472296935053719</v>
+        <v>-1.0679707468327556e-7</v>
       </c>
       <c r="J22">
-        <v>-2.074420824965576</v>
+        <v>-0.0002015345994363721</v>
       </c>
       <c r="K22">
-        <v>0.6276466448158264</v>
+        <v>2.5725171770376107</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-1.9892307391874384</v>
+        <v>-4.293894613684648e-8</v>
       </c>
       <c r="J23">
-        <v>-1.5386216619184865</v>
+        <v>-7.521398447537138e-5</v>
       </c>
       <c r="K23">
-        <v>1.4912178049856037</v>
+        <v>2.3677021885966365</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-0.7666671168628533</v>
+        <v>-2.4659624187579135e-8</v>
       </c>
       <c r="J24">
-        <v>-0.6055788072956889</v>
+        <v>-4.2620178074402814e-5</v>
       </c>
       <c r="K24">
-        <v>3.018018492296109</v>
+        <v>2.245483474661591</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-0.009673602850805298</v>
+        <v>-1.661774566089368e-8</v>
       </c>
       <c r="J25">
-        <v>-0.008711787501981486</v>
+        <v>-2.9363505882019157e-5</v>
       </c>
       <c r="K25">
-        <v>3.377746516065255</v>
+        <v>2.168900937839098</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-0.0008135365281527944</v>
+        <v>-9.679732909068279e-9</v>
       </c>
       <c r="J26">
-        <v>-0.0010417595277151877</v>
+        <v>-1.7389445560797322e-5</v>
       </c>
       <c r="K26">
-        <v>3.0045624413340124</v>
+        <v>2.0602752791436854</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-0.0003920105334659176</v>
+        <v>-6.801831764914868e-9</v>
       </c>
       <c r="J27">
-        <v>-0.0004887703989400115</v>
+        <v>-1.2357902351335093e-5</v>
       </c>
       <c r="K27">
-        <v>2.8406850887204302</v>
+        <v>1.9884881419829192</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-0.00018715507411818722</v>
+        <v>-5.978126278291936e-9</v>
       </c>
       <c r="J28">
-        <v>-0.00025489038089415754</v>
+        <v>-1.1107446966216633e-5</v>
       </c>
       <c r="K28">
-        <v>2.7148873156786046</v>
+        <v>1.9672984237049516</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-0.00013243677092479307</v>
+        <v>-6.0035881399881746e-9</v>
       </c>
       <c r="J29">
-        <v>-0.00017793035409573852</v>
+        <v>-1.1330428590051051e-5</v>
       </c>
       <c r="K29">
-        <v>2.636380414572587</v>
+        <v>1.9726927204048976</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-0.00011122067836066829</v>
+        <v>-3.7212533056309158e-9</v>
       </c>
       <c r="J30">
-        <v>-0.0001364107230135234</v>
+        <v>-6.974833261747841e-6</v>
       </c>
       <c r="K30">
-        <v>2.5607097053051744</v>
+        <v>1.8676659994741345</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-7.659636598321515e-5</v>
+        <v>-3.828108841988103e-9</v>
       </c>
       <c r="J31">
-        <v>-9.742290881904425e-5</v>
+        <v>-7.088223587388742e-6</v>
       </c>
       <c r="K31">
-        <v>2.4957409027906494</v>
+        <v>1.8701960813606615</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-6.335190243260694e-5</v>
+        <v>-3.3608725565119535e-9</v>
       </c>
       <c r="J32">
-        <v>-7.87418194861135e-5</v>
+        <v>-6.3987490064477775e-6</v>
       </c>
       <c r="K32">
-        <v>2.4451842725758475</v>
+        <v>1.8498308548126345</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_22.xlsx
+++ b/xls/square_un_16_tri3_22.xlsx
@@ -482,13 +482,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-7.728510017020902e-5</v>
+        <v>-1.6020100926020973</v>
       </c>
       <c r="J20">
-        <v>-0.23094000593717381</v>
+        <v>-1.3655569833008745</v>
       </c>
       <c r="K20">
-        <v>3.2357765754730337</v>
+        <v>1.2779335012301092</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -517,13 +517,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.1588589233589868e-5</v>
+        <v>-0.8755496833276348</v>
       </c>
       <c r="J21">
-        <v>-0.035195672959569886</v>
+        <v>-0.7509995215636593</v>
       </c>
       <c r="K21">
-        <v>3.3554678787833194</v>
+        <v>1.8292802468420382</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -552,13 +552,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-1.0679707468327556e-7</v>
+        <v>-0.017292714440521086</v>
       </c>
       <c r="J22">
-        <v>-0.0002015345994363721</v>
+        <v>-0.013648106278579816</v>
       </c>
       <c r="K22">
-        <v>2.5725171770376107</v>
+        <v>3.0105072862413613</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -587,13 +587,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-4.293894613684648e-8</v>
+        <v>-7.676632445067026e-5</v>
       </c>
       <c r="J23">
-        <v>-7.521398447537138e-5</v>
+        <v>-9.627358259687317e-5</v>
       </c>
       <c r="K23">
-        <v>2.3677021885966365</v>
+        <v>2.4872668217152634</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -622,13 +622,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-2.4659624187579135e-8</v>
+        <v>-5.63703808920858e-5</v>
       </c>
       <c r="J24">
-        <v>-4.2620178074402814e-5</v>
+        <v>-5.281073824964597e-5</v>
       </c>
       <c r="K24">
-        <v>2.245483474661591</v>
+        <v>2.2971243848939062</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-1.661774566089368e-8</v>
+        <v>-3.810482118775902e-5</v>
       </c>
       <c r="J25">
-        <v>-2.9363505882019157e-5</v>
+        <v>-3.5605489825729763e-5</v>
       </c>
       <c r="K25">
-        <v>2.168900937839098</v>
+        <v>2.2095132931140804</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -692,13 +692,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-9.679732909068279e-9</v>
+        <v>-1.5201513902113884e-5</v>
       </c>
       <c r="J26">
-        <v>-1.7389445560797322e-5</v>
+        <v>-1.6756399026207357e-5</v>
       </c>
       <c r="K26">
-        <v>2.0602752791436854</v>
+        <v>2.0870589660654066</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -727,13 +727,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-6.801831764914868e-9</v>
+        <v>-1.2790338137016311e-5</v>
       </c>
       <c r="J27">
-        <v>-1.2357902351335093e-5</v>
+        <v>-1.2794193872831351e-5</v>
       </c>
       <c r="K27">
-        <v>1.9884881419829192</v>
+        <v>2.004512930588732</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -762,13 +762,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-5.978126278291936e-9</v>
+        <v>-1.208287854322052e-5</v>
       </c>
       <c r="J28">
-        <v>-1.1107446966216633e-5</v>
+        <v>-1.1930484226852521e-5</v>
       </c>
       <c r="K28">
-        <v>1.9672984237049516</v>
+        <v>1.9848524814587716</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -797,13 +797,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-6.0035881399881746e-9</v>
+        <v>-1.2521421905821043e-5</v>
       </c>
       <c r="J29">
-        <v>-1.1330428590051051e-5</v>
+        <v>-1.217647129598684e-5</v>
       </c>
       <c r="K29">
-        <v>1.9726927204048976</v>
+        <v>1.9854386176928163</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -832,13 +832,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-3.7212533056309158e-9</v>
+        <v>-7.1208177427581214e-6</v>
       </c>
       <c r="J30">
-        <v>-6.974833261747841e-6</v>
+        <v>-7.193474193749356e-6</v>
       </c>
       <c r="K30">
-        <v>1.8676659994741345</v>
+        <v>1.8808773522616082</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -867,13 +867,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-3.828108841988103e-9</v>
+        <v>-8.340976918976222e-6</v>
       </c>
       <c r="J31">
-        <v>-7.088223587388742e-6</v>
+        <v>-7.818235366695208e-6</v>
       </c>
       <c r="K31">
-        <v>1.8701960813606615</v>
+        <v>1.8796354332625387</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -902,13 +902,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-3.3608725565119535e-9</v>
+        <v>-7.5158480329465075e-6</v>
       </c>
       <c r="J32">
-        <v>-6.3987490064477775e-6</v>
+        <v>-7.0995509395465054e-6</v>
       </c>
       <c r="K32">
-        <v>1.8498308548126345</v>
+        <v>1.8598485700593448</v>
       </c>
     </row>
   </sheetData>
